--- a/public/plantilla-acciones-amb.xlsx
+++ b/public/plantilla-acciones-amb.xlsx
@@ -15,6 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="#,##0.##"/>
+  </numFmts>
   <fonts count="17">
     <font>
       <name val="Calibri"/>

--- a/public/plantilla-acciones-amb.xlsx
+++ b/public/plantilla-acciones-amb.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="3" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones Correctivas Amb." sheetId="1" state="visible" r:id="rId1"/>

--- a/public/plantilla-acciones-amb.xlsx
+++ b/public/plantilla-acciones-amb.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones Correctivas Amb." sheetId="1" state="visible" r:id="rId1"/>
@@ -16,9 +16,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="#,##0.##"/>
+    <numFmt numFmtId="164" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -140,6 +140,10 @@
       <family val="2"/>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="7">
@@ -388,7 +392,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -428,7 +432,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="16" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -507,7 +511,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -522,7 +526,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -533,6 +537,49 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1818,6 +1865,74 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -2340,20 +2455,20 @@
       </c>
       <c r="B11" s="25" t="n"/>
       <c r="C11" s="26" t="n"/>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="25" t="n"/>
-      <c r="F11" s="26" t="n"/>
+      <c r="D11" s="57" t="n"/>
+      <c r="E11" s="58" t="n"/>
+      <c r="F11" s="59" t="n"/>
       <c r="G11" s="27" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
       <c r="H11" s="26" t="n"/>
-      <c r="I11" s="24" t="n"/>
-      <c r="J11" s="25" t="n"/>
-      <c r="K11" s="25" t="n"/>
-      <c r="L11" s="25" t="n"/>
-      <c r="M11" s="26" t="n"/>
+      <c r="I11" s="57" t="n"/>
+      <c r="J11" s="58" t="n"/>
+      <c r="K11" s="58" t="n"/>
+      <c r="L11" s="58" t="n"/>
+      <c r="M11" s="59" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="34">
       <c r="A12" s="27" t="inlineStr">
@@ -2363,20 +2478,20 @@
       </c>
       <c r="B12" s="25" t="n"/>
       <c r="C12" s="26" t="n"/>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="26" t="n"/>
+      <c r="D12" s="57" t="n"/>
+      <c r="E12" s="58" t="n"/>
+      <c r="F12" s="59" t="n"/>
       <c r="G12" s="27" t="inlineStr">
         <is>
           <t>Responsable del seguimiento</t>
         </is>
       </c>
       <c r="H12" s="26" t="n"/>
-      <c r="I12" s="24" t="n"/>
-      <c r="J12" s="25" t="n"/>
-      <c r="K12" s="25" t="n"/>
-      <c r="L12" s="25" t="n"/>
-      <c r="M12" s="26" t="n"/>
+      <c r="I12" s="57" t="n"/>
+      <c r="J12" s="58" t="n"/>
+      <c r="K12" s="58" t="n"/>
+      <c r="L12" s="58" t="n"/>
+      <c r="M12" s="59" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="34">
       <c r="A13" s="27" t="inlineStr">
@@ -2386,20 +2501,20 @@
       </c>
       <c r="B13" s="25" t="n"/>
       <c r="C13" s="26" t="n"/>
-      <c r="D13" s="51" t="n"/>
+      <c r="D13" s="60" t="n"/>
       <c r="E13" s="27" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="F13" s="49" t="n"/>
+      <c r="F13" s="61" t="n"/>
       <c r="G13" s="27" t="inlineStr">
         <is>
           <t>Hoja N°</t>
         </is>
       </c>
       <c r="H13" s="26" t="n"/>
-      <c r="I13" s="49" t="n"/>
+      <c r="I13" s="61" t="n"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="34">
       <c r="A14" s="21" t="inlineStr">
@@ -2488,174 +2603,174 @@
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" s="34">
-      <c r="A16" s="55" t="n">
+      <c r="A16" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="54" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="47" t="n"/>
-      <c r="E16" s="47" t="n"/>
-      <c r="F16" s="47" t="n"/>
-      <c r="G16" s="55" t="n"/>
-      <c r="H16" s="47" t="n"/>
-      <c r="I16" s="54" t="n"/>
-      <c r="J16" s="55" t="n"/>
-      <c r="K16" s="54" t="n"/>
-      <c r="L16" s="55" t="n"/>
-      <c r="M16" s="47" t="n"/>
+      <c r="B16" s="63" t="n"/>
+      <c r="C16" s="64" t="n"/>
+      <c r="D16" s="65" t="n"/>
+      <c r="E16" s="65" t="n"/>
+      <c r="F16" s="65" t="n"/>
+      <c r="G16" s="66" t="n"/>
+      <c r="H16" s="65" t="n"/>
+      <c r="I16" s="63" t="n"/>
+      <c r="J16" s="66" t="n"/>
+      <c r="K16" s="63" t="n"/>
+      <c r="L16" s="66" t="n"/>
+      <c r="M16" s="65" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1" s="34">
-      <c r="A17" s="55" t="n">
+      <c r="A17" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="54" t="n"/>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="47" t="n"/>
-      <c r="E17" s="47" t="n"/>
-      <c r="F17" s="47" t="n"/>
-      <c r="G17" s="55" t="n"/>
-      <c r="H17" s="47" t="n"/>
-      <c r="I17" s="54" t="n"/>
-      <c r="J17" s="55" t="n"/>
-      <c r="K17" s="54" t="n"/>
-      <c r="L17" s="55" t="n"/>
-      <c r="M17" s="47" t="n"/>
+      <c r="B17" s="63" t="n"/>
+      <c r="C17" s="64" t="n"/>
+      <c r="D17" s="65" t="n"/>
+      <c r="E17" s="65" t="n"/>
+      <c r="F17" s="65" t="n"/>
+      <c r="G17" s="66" t="n"/>
+      <c r="H17" s="65" t="n"/>
+      <c r="I17" s="63" t="n"/>
+      <c r="J17" s="66" t="n"/>
+      <c r="K17" s="63" t="n"/>
+      <c r="L17" s="66" t="n"/>
+      <c r="M17" s="65" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1" s="34">
-      <c r="A18" s="55" t="n">
+      <c r="A18" s="62" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="54" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="47" t="n"/>
-      <c r="E18" s="47" t="n"/>
-      <c r="F18" s="47" t="n"/>
-      <c r="G18" s="55" t="n"/>
-      <c r="H18" s="47" t="n"/>
-      <c r="I18" s="54" t="n"/>
-      <c r="J18" s="55" t="n"/>
-      <c r="K18" s="54" t="n"/>
-      <c r="L18" s="55" t="n"/>
-      <c r="M18" s="47" t="n"/>
+      <c r="B18" s="63" t="n"/>
+      <c r="C18" s="64" t="n"/>
+      <c r="D18" s="65" t="n"/>
+      <c r="E18" s="65" t="n"/>
+      <c r="F18" s="65" t="n"/>
+      <c r="G18" s="66" t="n"/>
+      <c r="H18" s="65" t="n"/>
+      <c r="I18" s="63" t="n"/>
+      <c r="J18" s="66" t="n"/>
+      <c r="K18" s="63" t="n"/>
+      <c r="L18" s="66" t="n"/>
+      <c r="M18" s="65" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1" s="34">
-      <c r="A19" s="55" t="n">
+      <c r="A19" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="54" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="47" t="n"/>
-      <c r="E19" s="47" t="n"/>
-      <c r="F19" s="47" t="n"/>
-      <c r="G19" s="55" t="n"/>
-      <c r="H19" s="47" t="n"/>
-      <c r="I19" s="54" t="n"/>
-      <c r="J19" s="55" t="n"/>
-      <c r="K19" s="54" t="n"/>
-      <c r="L19" s="55" t="n"/>
-      <c r="M19" s="47" t="n"/>
+      <c r="B19" s="63" t="n"/>
+      <c r="C19" s="64" t="n"/>
+      <c r="D19" s="65" t="n"/>
+      <c r="E19" s="65" t="n"/>
+      <c r="F19" s="65" t="n"/>
+      <c r="G19" s="66" t="n"/>
+      <c r="H19" s="65" t="n"/>
+      <c r="I19" s="63" t="n"/>
+      <c r="J19" s="66" t="n"/>
+      <c r="K19" s="63" t="n"/>
+      <c r="L19" s="66" t="n"/>
+      <c r="M19" s="65" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1" s="34">
-      <c r="A20" s="55" t="n">
+      <c r="A20" s="62" t="n">
         <v>5</v>
       </c>
-      <c r="B20" s="54" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="47" t="n"/>
-      <c r="E20" s="47" t="n"/>
-      <c r="F20" s="47" t="n"/>
-      <c r="G20" s="55" t="n"/>
-      <c r="H20" s="47" t="n"/>
-      <c r="I20" s="54" t="n"/>
-      <c r="J20" s="55" t="n"/>
-      <c r="K20" s="54" t="n"/>
-      <c r="L20" s="55" t="n"/>
-      <c r="M20" s="47" t="n"/>
+      <c r="B20" s="63" t="n"/>
+      <c r="C20" s="64" t="n"/>
+      <c r="D20" s="65" t="n"/>
+      <c r="E20" s="65" t="n"/>
+      <c r="F20" s="65" t="n"/>
+      <c r="G20" s="66" t="n"/>
+      <c r="H20" s="65" t="n"/>
+      <c r="I20" s="63" t="n"/>
+      <c r="J20" s="66" t="n"/>
+      <c r="K20" s="63" t="n"/>
+      <c r="L20" s="66" t="n"/>
+      <c r="M20" s="65" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1" s="34">
-      <c r="A21" s="55" t="n">
+      <c r="A21" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="B21" s="54" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="47" t="n"/>
-      <c r="E21" s="47" t="n"/>
-      <c r="F21" s="47" t="n"/>
-      <c r="G21" s="55" t="n"/>
-      <c r="H21" s="47" t="n"/>
-      <c r="I21" s="54" t="n"/>
-      <c r="J21" s="55" t="n"/>
-      <c r="K21" s="54" t="n"/>
-      <c r="L21" s="55" t="n"/>
-      <c r="M21" s="47" t="n"/>
+      <c r="B21" s="63" t="n"/>
+      <c r="C21" s="64" t="n"/>
+      <c r="D21" s="65" t="n"/>
+      <c r="E21" s="65" t="n"/>
+      <c r="F21" s="65" t="n"/>
+      <c r="G21" s="66" t="n"/>
+      <c r="H21" s="65" t="n"/>
+      <c r="I21" s="63" t="n"/>
+      <c r="J21" s="66" t="n"/>
+      <c r="K21" s="63" t="n"/>
+      <c r="L21" s="66" t="n"/>
+      <c r="M21" s="65" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1" s="34">
-      <c r="A22" s="55" t="n">
+      <c r="A22" s="62" t="n">
         <v>7</v>
       </c>
-      <c r="B22" s="54" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="47" t="n"/>
-      <c r="E22" s="47" t="n"/>
-      <c r="F22" s="47" t="n"/>
-      <c r="G22" s="55" t="n"/>
-      <c r="H22" s="47" t="n"/>
-      <c r="I22" s="54" t="n"/>
-      <c r="J22" s="55" t="n"/>
-      <c r="K22" s="54" t="n"/>
-      <c r="L22" s="55" t="n"/>
-      <c r="M22" s="47" t="n"/>
+      <c r="B22" s="63" t="n"/>
+      <c r="C22" s="64" t="n"/>
+      <c r="D22" s="65" t="n"/>
+      <c r="E22" s="65" t="n"/>
+      <c r="F22" s="65" t="n"/>
+      <c r="G22" s="66" t="n"/>
+      <c r="H22" s="65" t="n"/>
+      <c r="I22" s="63" t="n"/>
+      <c r="J22" s="66" t="n"/>
+      <c r="K22" s="63" t="n"/>
+      <c r="L22" s="66" t="n"/>
+      <c r="M22" s="65" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1" s="34">
-      <c r="A23" s="55" t="n">
+      <c r="A23" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="54" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="47" t="n"/>
-      <c r="E23" s="47" t="n"/>
-      <c r="F23" s="47" t="n"/>
-      <c r="G23" s="55" t="n"/>
-      <c r="H23" s="47" t="n"/>
-      <c r="I23" s="54" t="n"/>
-      <c r="J23" s="55" t="n"/>
-      <c r="K23" s="54" t="n"/>
-      <c r="L23" s="55" t="n"/>
-      <c r="M23" s="47" t="n"/>
+      <c r="B23" s="63" t="n"/>
+      <c r="C23" s="64" t="n"/>
+      <c r="D23" s="65" t="n"/>
+      <c r="E23" s="65" t="n"/>
+      <c r="F23" s="65" t="n"/>
+      <c r="G23" s="66" t="n"/>
+      <c r="H23" s="65" t="n"/>
+      <c r="I23" s="63" t="n"/>
+      <c r="J23" s="66" t="n"/>
+      <c r="K23" s="63" t="n"/>
+      <c r="L23" s="66" t="n"/>
+      <c r="M23" s="65" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1" s="34">
-      <c r="A24" s="55" t="n">
+      <c r="A24" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="B24" s="54" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="47" t="n"/>
-      <c r="E24" s="47" t="n"/>
-      <c r="F24" s="47" t="n"/>
-      <c r="G24" s="55" t="n"/>
-      <c r="H24" s="47" t="n"/>
-      <c r="I24" s="54" t="n"/>
-      <c r="J24" s="55" t="n"/>
-      <c r="K24" s="54" t="n"/>
-      <c r="L24" s="55" t="n"/>
-      <c r="M24" s="47" t="n"/>
+      <c r="B24" s="63" t="n"/>
+      <c r="C24" s="64" t="n"/>
+      <c r="D24" s="65" t="n"/>
+      <c r="E24" s="65" t="n"/>
+      <c r="F24" s="65" t="n"/>
+      <c r="G24" s="66" t="n"/>
+      <c r="H24" s="65" t="n"/>
+      <c r="I24" s="63" t="n"/>
+      <c r="J24" s="66" t="n"/>
+      <c r="K24" s="63" t="n"/>
+      <c r="L24" s="66" t="n"/>
+      <c r="M24" s="65" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1" s="34">
-      <c r="A25" s="55" t="n">
+      <c r="A25" s="62" t="n">
         <v>10</v>
       </c>
-      <c r="B25" s="54" t="n"/>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="47" t="n"/>
-      <c r="E25" s="47" t="n"/>
-      <c r="F25" s="47" t="n"/>
-      <c r="G25" s="55" t="n"/>
-      <c r="H25" s="47" t="n"/>
-      <c r="I25" s="54" t="n"/>
-      <c r="J25" s="55" t="n"/>
-      <c r="K25" s="54" t="n"/>
-      <c r="L25" s="55" t="n"/>
-      <c r="M25" s="47" t="n"/>
+      <c r="B25" s="63" t="n"/>
+      <c r="C25" s="64" t="n"/>
+      <c r="D25" s="65" t="n"/>
+      <c r="E25" s="65" t="n"/>
+      <c r="F25" s="65" t="n"/>
+      <c r="G25" s="66" t="n"/>
+      <c r="H25" s="65" t="n"/>
+      <c r="I25" s="63" t="n"/>
+      <c r="J25" s="66" t="n"/>
+      <c r="K25" s="63" t="n"/>
+      <c r="L25" s="66" t="n"/>
+      <c r="M25" s="65" t="n"/>
     </row>
     <row r="26" ht="19.95" customHeight="1" s="34">
       <c r="A26" s="40" t="inlineStr">
@@ -2791,25 +2906,25 @@
         </is>
       </c>
       <c r="B31" s="23" t="n"/>
-      <c r="C31" s="29" t="n"/>
-      <c r="D31" s="22" t="n"/>
-      <c r="E31" s="23" t="n"/>
+      <c r="C31" s="65" t="n"/>
+      <c r="D31" s="67" t="n"/>
+      <c r="E31" s="68" t="n"/>
       <c r="F31" s="38" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="G31" s="23" t="n"/>
-      <c r="H31" s="29" t="n"/>
-      <c r="I31" s="23" t="n"/>
+      <c r="H31" s="65" t="n"/>
+      <c r="I31" s="68" t="n"/>
       <c r="J31" s="38" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="K31" s="23" t="n"/>
-      <c r="L31" s="29" t="n"/>
-      <c r="M31" s="23" t="n"/>
+      <c r="L31" s="65" t="n"/>
+      <c r="M31" s="68" t="n"/>
     </row>
     <row r="32" ht="21" customHeight="1" s="34">
       <c r="A32" s="38" t="inlineStr">
@@ -2818,25 +2933,25 @@
         </is>
       </c>
       <c r="B32" s="23" t="n"/>
-      <c r="C32" s="29" t="n"/>
-      <c r="D32" s="22" t="n"/>
-      <c r="E32" s="23" t="n"/>
+      <c r="C32" s="65" t="n"/>
+      <c r="D32" s="67" t="n"/>
+      <c r="E32" s="68" t="n"/>
       <c r="F32" s="38" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="G32" s="23" t="n"/>
-      <c r="H32" s="29" t="n"/>
-      <c r="I32" s="23" t="n"/>
+      <c r="H32" s="65" t="n"/>
+      <c r="I32" s="68" t="n"/>
       <c r="J32" s="38" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="K32" s="23" t="n"/>
-      <c r="L32" s="29" t="n"/>
-      <c r="M32" s="23" t="n"/>
+      <c r="L32" s="65" t="n"/>
+      <c r="M32" s="68" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1" s="34">
       <c r="A33" s="38" t="inlineStr">
@@ -2845,25 +2960,25 @@
         </is>
       </c>
       <c r="B33" s="23" t="n"/>
-      <c r="C33" s="29" t="n"/>
-      <c r="D33" s="22" t="n"/>
-      <c r="E33" s="23" t="n"/>
+      <c r="C33" s="65" t="n"/>
+      <c r="D33" s="67" t="n"/>
+      <c r="E33" s="68" t="n"/>
       <c r="F33" s="38" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="G33" s="23" t="n"/>
-      <c r="H33" s="29" t="n"/>
-      <c r="I33" s="23" t="n"/>
+      <c r="H33" s="65" t="n"/>
+      <c r="I33" s="68" t="n"/>
       <c r="J33" s="38" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="K33" s="23" t="n"/>
-      <c r="L33" s="29" t="n"/>
-      <c r="M33" s="23" t="n"/>
+      <c r="L33" s="65" t="n"/>
+      <c r="M33" s="68" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -2877,6 +2992,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="50">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A14:M14"/>
